--- a/Normalisasi_SalesDB_Fran Dello.xlsx
+++ b/Normalisasi_SalesDB_Fran Dello.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Kerjaan\MII\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D211A974-8A7A-48B7-A6C2-86B0105722D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75741533-A44E-4937-90E3-9C40FA5CCC4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Petunjuk" sheetId="1" r:id="rId1"/>
@@ -86,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="149">
   <si>
     <t>Latihan Normalisasi SalesDB — dari data faktur (UNF) sampai 3NF</t>
   </si>
@@ -504,6 +504,74 @@
   </si>
   <si>
     <t>375.000</t>
+  </si>
+  <si>
+    <t>TABLE INVOICE</t>
+  </si>
+  <si>
+    <t>TABLE PELANGGAN</t>
+  </si>
+  <si>
+    <t>TABLE PRODUK</t>
+  </si>
+  <si>
+    <t>TABLE KATEGORI</t>
+  </si>
+  <si>
+    <t>TABLE TRANSAKSI</t>
+  </si>
+  <si>
+    <t>Kode Transaksi</t>
+  </si>
+  <si>
+    <t>T01</t>
+  </si>
+  <si>
+    <t>T02</t>
+  </si>
+  <si>
+    <t>T04</t>
+  </si>
+  <si>
+    <t>T03</t>
+  </si>
+  <si>
+    <t>T05</t>
+  </si>
+  <si>
+    <t>T06</t>
+  </si>
+  <si>
+    <t>T07</t>
+  </si>
+  <si>
+    <t>T08</t>
+  </si>
+  <si>
+    <t>T09</t>
+  </si>
+  <si>
+    <t>T10</t>
+  </si>
+  <si>
+    <t>T11</t>
+  </si>
+  <si>
+    <t>T12</t>
+  </si>
+  <si>
+    <t>Saya membuat table transaksi untuk menyimpan data pembelian pelanggan dan barang yang dibeli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Faktur, Kode Pelanggan, Kode Produk, Kode Kategori, Kode Transaksi
+</t>
+  </si>
+  <si>
+    <t>No Faktur -&gt; Tanggal (Partial)
+Kode Pelanggan -&gt; Nama Pelanggan, Email, Kota (Partial)
+Kode Produk -&gt; Nama Produk, Harga Satuan (Rp) (Partial)
+Kode Kategori -&gt; Nama Kategori (Partial)
+Kode Transaksi -&gt; Qty (Partial)</t>
   </si>
 </sst>
 </file>
@@ -511,9 +579,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="dd\-mm\-yyyy"/>
+    <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -589,8 +657,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -622,8 +704,20 @@
         <fgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -646,11 +740,65 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -668,7 +816,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -678,17 +826,10 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -703,6 +844,53 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1456,36 +1644,36 @@
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="42" t="s">
         <v>101</v>
       </c>
-      <c r="B13" s="20"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A14" s="21" t="s">
+      <c r="A14" s="43" t="s">
         <v>102</v>
       </c>
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
+      <c r="B14" s="43"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="B15" s="22"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="B16" s="23"/>
-      <c r="C16" s="23"/>
-      <c r="D16" s="23"/>
+      <c r="B16" s="44"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1559,10 +1747,10 @@
       </c>
     </row>
     <row r="8" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="26" t="s">
+      <c r="A8" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="22" t="s">
         <v>122</v>
       </c>
     </row>
@@ -1613,13 +1801,13 @@
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A12" s="28" t="s">
+      <c r="A12" s="25" t="s">
         <v>35</v>
       </c>
       <c r="B12" s="13">
         <v>46266</v>
       </c>
-      <c r="C12" s="28" t="s">
+      <c r="C12" s="25" t="s">
         <v>36</v>
       </c>
       <c r="D12" s="12" t="s">
@@ -1631,22 +1819,22 @@
       <c r="F12" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="G12" s="28" t="s">
+      <c r="G12" s="25" t="s">
         <v>107</v>
       </c>
       <c r="H12" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="I12" s="28" t="s">
+      <c r="I12" s="25" t="s">
         <v>64</v>
       </c>
       <c r="J12" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="K12" s="24">
+      <c r="K12" s="21">
         <v>1</v>
       </c>
-      <c r="L12" s="27" t="s">
+      <c r="L12" s="24" t="s">
         <v>112</v>
       </c>
       <c r="M12" s="14">
@@ -1654,13 +1842,13 @@
       </c>
     </row>
     <row r="13" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="28" t="s">
+      <c r="A13" s="25" t="s">
         <v>35</v>
       </c>
       <c r="B13" s="13">
         <v>46266</v>
       </c>
-      <c r="C13" s="28" t="s">
+      <c r="C13" s="25" t="s">
         <v>36</v>
       </c>
       <c r="D13" s="12" t="s">
@@ -1672,22 +1860,22 @@
       <c r="F13" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="G13" s="28" t="s">
+      <c r="G13" s="25" t="s">
         <v>106</v>
       </c>
       <c r="H13" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="I13" s="28" t="s">
+      <c r="I13" s="25" t="s">
         <v>110</v>
       </c>
       <c r="J13" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="K13" s="24">
+      <c r="K13" s="21">
         <v>2</v>
       </c>
-      <c r="L13" s="27" t="s">
+      <c r="L13" s="24" t="s">
         <v>123</v>
       </c>
       <c r="M13" s="14">
@@ -1695,13 +1883,13 @@
       </c>
     </row>
     <row r="14" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="28" t="s">
+      <c r="A14" s="25" t="s">
         <v>46</v>
       </c>
       <c r="B14" s="13">
         <v>46275</v>
       </c>
-      <c r="C14" s="28" t="s">
+      <c r="C14" s="25" t="s">
         <v>47</v>
       </c>
       <c r="D14" s="12" t="s">
@@ -1713,22 +1901,22 @@
       <c r="F14" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="G14" s="28" t="s">
+      <c r="G14" s="25" t="s">
         <v>113</v>
       </c>
       <c r="H14" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="I14" s="28" t="s">
+      <c r="I14" s="25" t="s">
         <v>110</v>
       </c>
       <c r="J14" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="K14" s="24">
+      <c r="K14" s="21">
         <v>1</v>
       </c>
-      <c r="L14" s="27" t="s">
+      <c r="L14" s="24" t="s">
         <v>124</v>
       </c>
       <c r="M14" s="14">
@@ -1736,13 +1924,13 @@
       </c>
     </row>
     <row r="15" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="28" t="s">
+      <c r="A15" s="25" t="s">
         <v>46</v>
       </c>
       <c r="B15" s="13">
         <v>46275</v>
       </c>
-      <c r="C15" s="28" t="s">
+      <c r="C15" s="25" t="s">
         <v>47</v>
       </c>
       <c r="D15" s="12" t="s">
@@ -1754,22 +1942,22 @@
       <c r="F15" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="G15" s="28" t="s">
+      <c r="G15" s="25" t="s">
         <v>106</v>
       </c>
       <c r="H15" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="I15" s="28" t="s">
+      <c r="I15" s="25" t="s">
         <v>110</v>
       </c>
       <c r="J15" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="K15" s="24">
+      <c r="K15" s="21">
         <v>1</v>
       </c>
-      <c r="L15" s="27" t="s">
+      <c r="L15" s="24" t="s">
         <v>123</v>
       </c>
       <c r="M15" s="14">
@@ -1777,13 +1965,13 @@
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="25" t="s">
         <v>57</v>
       </c>
       <c r="B16" s="13">
         <v>46277</v>
       </c>
-      <c r="C16" s="28" t="s">
+      <c r="C16" s="25" t="s">
         <v>58</v>
       </c>
       <c r="D16" s="12" t="s">
@@ -1795,13 +1983,13 @@
       <c r="F16" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="G16" s="28" t="s">
+      <c r="G16" s="25" t="s">
         <v>62</v>
       </c>
       <c r="H16" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="I16" s="28" t="s">
+      <c r="I16" s="25" t="s">
         <v>64</v>
       </c>
       <c r="J16" s="12" t="s">
@@ -1810,7 +1998,7 @@
       <c r="K16" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="L16" s="27" t="s">
+      <c r="L16" s="24" t="s">
         <v>67</v>
       </c>
       <c r="M16" s="14">
@@ -1818,13 +2006,13 @@
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A17" s="28" t="s">
+      <c r="A17" s="25" t="s">
         <v>68</v>
       </c>
       <c r="B17" s="13">
         <v>46280</v>
       </c>
-      <c r="C17" s="28" t="s">
+      <c r="C17" s="25" t="s">
         <v>36</v>
       </c>
       <c r="D17" s="12" t="s">
@@ -1836,22 +2024,22 @@
       <c r="F17" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="G17" s="28" t="s">
+      <c r="G17" s="25" t="s">
         <v>115</v>
       </c>
       <c r="H17" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="I17" s="28" t="s">
+      <c r="I17" s="25" t="s">
         <v>119</v>
       </c>
       <c r="J17" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="K17" s="24">
+      <c r="K17" s="21">
         <v>10</v>
       </c>
-      <c r="L17" s="27" t="s">
+      <c r="L17" s="24" t="s">
         <v>125</v>
       </c>
       <c r="M17" s="14">
@@ -1859,13 +2047,13 @@
       </c>
     </row>
     <row r="18" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="28" t="s">
+      <c r="A18" s="25" t="s">
         <v>68</v>
       </c>
       <c r="B18" s="13">
         <v>46280</v>
       </c>
-      <c r="C18" s="28" t="s">
+      <c r="C18" s="25" t="s">
         <v>36</v>
       </c>
       <c r="D18" s="12" t="s">
@@ -1877,22 +2065,22 @@
       <c r="F18" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="G18" s="28" t="s">
+      <c r="G18" s="25" t="s">
         <v>116</v>
       </c>
       <c r="H18" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="I18" s="28" t="s">
+      <c r="I18" s="25" t="s">
         <v>119</v>
       </c>
       <c r="J18" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="K18" s="24">
+      <c r="K18" s="21">
         <v>2</v>
       </c>
-      <c r="L18" s="27" t="s">
+      <c r="L18" s="24" t="s">
         <v>126</v>
       </c>
       <c r="M18" s="14">
@@ -1900,13 +2088,13 @@
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A19" s="28" t="s">
+      <c r="A19" s="25" t="s">
         <v>75</v>
       </c>
       <c r="B19" s="13">
         <v>46283</v>
       </c>
-      <c r="C19" s="28" t="s">
+      <c r="C19" s="25" t="s">
         <v>47</v>
       </c>
       <c r="D19" s="12" t="s">
@@ -1918,22 +2106,22 @@
       <c r="F19" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="G19" s="28" t="s">
+      <c r="G19" s="25" t="s">
         <v>62</v>
       </c>
       <c r="H19" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="I19" s="28" t="s">
+      <c r="I19" s="25" t="s">
         <v>64</v>
       </c>
       <c r="J19" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="K19" s="24">
+      <c r="K19" s="21">
         <v>1</v>
       </c>
-      <c r="L19" s="27" t="s">
+      <c r="L19" s="24" t="s">
         <v>127</v>
       </c>
       <c r="M19" s="14">
@@ -1941,13 +2129,13 @@
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A20" s="28" t="s">
+      <c r="A20" s="25" t="s">
         <v>75</v>
       </c>
       <c r="B20" s="13">
         <v>46283</v>
       </c>
-      <c r="C20" s="28" t="s">
+      <c r="C20" s="25" t="s">
         <v>47</v>
       </c>
       <c r="D20" s="12" t="s">
@@ -1959,22 +2147,22 @@
       <c r="F20" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="G20" s="28" t="s">
+      <c r="G20" s="25" t="s">
         <v>115</v>
       </c>
       <c r="H20" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="I20" s="28" t="s">
+      <c r="I20" s="25" t="s">
         <v>119</v>
       </c>
       <c r="J20" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="K20" s="24">
+      <c r="K20" s="21">
         <v>5</v>
       </c>
-      <c r="L20" s="27" t="s">
+      <c r="L20" s="24" t="s">
         <v>125</v>
       </c>
       <c r="M20" s="14">
@@ -1982,13 +2170,13 @@
       </c>
     </row>
     <row r="21" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="28" t="s">
+      <c r="A21" s="25" t="s">
         <v>75</v>
       </c>
       <c r="B21" s="13">
         <v>46283</v>
       </c>
-      <c r="C21" s="28" t="s">
+      <c r="C21" s="25" t="s">
         <v>47</v>
       </c>
       <c r="D21" s="12" t="s">
@@ -2000,22 +2188,22 @@
       <c r="F21" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="G21" s="28" t="s">
+      <c r="G21" s="25" t="s">
         <v>116</v>
       </c>
       <c r="H21" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="I21" s="28" t="s">
+      <c r="I21" s="25" t="s">
         <v>119</v>
       </c>
       <c r="J21" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="K21" s="24">
+      <c r="K21" s="21">
         <v>1</v>
       </c>
-      <c r="L21" s="27" t="s">
+      <c r="L21" s="24" t="s">
         <v>126</v>
       </c>
       <c r="M21" s="14">
@@ -2023,13 +2211,13 @@
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A22" s="28" t="s">
+      <c r="A22" s="25" t="s">
         <v>82</v>
       </c>
       <c r="B22" s="13">
         <v>46285</v>
       </c>
-      <c r="C22" s="28" t="s">
+      <c r="C22" s="25" t="s">
         <v>58</v>
       </c>
       <c r="D22" s="12" t="s">
@@ -2041,22 +2229,22 @@
       <c r="F22" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="G22" s="28" t="s">
+      <c r="G22" s="25" t="s">
         <v>107</v>
       </c>
       <c r="H22" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="I22" s="28" t="s">
+      <c r="I22" s="25" t="s">
         <v>64</v>
       </c>
       <c r="J22" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="K22" s="24">
+      <c r="K22" s="21">
         <v>2</v>
       </c>
-      <c r="L22" s="27" t="s">
+      <c r="L22" s="24" t="s">
         <v>112</v>
       </c>
       <c r="M22" s="14">
@@ -2064,13 +2252,13 @@
       </c>
     </row>
     <row r="23" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="28" t="s">
+      <c r="A23" s="25" t="s">
         <v>82</v>
       </c>
       <c r="B23" s="13">
         <v>46285</v>
       </c>
-      <c r="C23" s="28" t="s">
+      <c r="C23" s="25" t="s">
         <v>58</v>
       </c>
       <c r="D23" s="12" t="s">
@@ -2082,22 +2270,22 @@
       <c r="F23" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="G23" s="28" t="s">
+      <c r="G23" s="25" t="s">
         <v>113</v>
       </c>
       <c r="H23" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="I23" s="28" t="s">
+      <c r="I23" s="25" t="s">
         <v>110</v>
       </c>
       <c r="J23" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="K23" s="24">
+      <c r="K23" s="21">
         <v>1</v>
       </c>
-      <c r="L23" s="27" t="s">
+      <c r="L23" s="24" t="s">
         <v>124</v>
       </c>
       <c r="M23" s="14">
@@ -2114,67 +2302,547 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="11.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="16"/>
+      <c r="B6" s="22" t="s">
+        <v>147</v>
+      </c>
       <c r="C6" s="17" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="B7" s="16"/>
+      <c r="B7" s="22" t="s">
+        <v>148</v>
+      </c>
       <c r="C7" s="17" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="B8" s="16"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B8" s="22" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="18"/>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="26" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="D13" s="28"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="31">
+        <v>46266</v>
+      </c>
+      <c r="C14" s="32" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" s="31">
+        <v>46275</v>
+      </c>
+      <c r="C15" s="32" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16" s="31">
+        <v>46277</v>
+      </c>
+      <c r="C16" s="32" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="B17" s="31">
+        <v>46280</v>
+      </c>
+      <c r="C17" s="32" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="B18" s="31">
+        <v>46283</v>
+      </c>
+      <c r="C18" s="32" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="30" t="s">
+        <v>82</v>
+      </c>
+      <c r="B19" s="31">
+        <v>46285</v>
+      </c>
+      <c r="C19" s="32" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="27" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="D22" s="29" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="D23" s="37" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" s="41" t="s">
+        <v>49</v>
+      </c>
+      <c r="D24" s="41" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="B25" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="D25" s="37" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="40"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="38" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="D28" s="29" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="B29" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="C29" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="D29" s="32" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="B30" s="37" t="s">
+        <v>63</v>
+      </c>
+      <c r="C30" s="39" t="s">
+        <v>67</v>
+      </c>
+      <c r="D30" s="32" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="30" t="s">
+        <v>115</v>
+      </c>
+      <c r="B31" s="37" t="s">
+        <v>117</v>
+      </c>
+      <c r="C31" s="39" t="s">
+        <v>125</v>
+      </c>
+      <c r="D31" s="32" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="30" t="s">
+        <v>116</v>
+      </c>
+      <c r="B32" s="37" t="s">
+        <v>118</v>
+      </c>
+      <c r="C32" s="39" t="s">
+        <v>126</v>
+      </c>
+      <c r="D32" s="32" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="B33" s="37" t="s">
+        <v>109</v>
+      </c>
+      <c r="C33" s="39" t="s">
+        <v>123</v>
+      </c>
+      <c r="D33" s="32" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="B34" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="C34" s="39" t="s">
+        <v>124</v>
+      </c>
+      <c r="D34" s="32" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="27" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="B37" s="29" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="B38" s="37" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="B39" s="37" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="B40" s="37" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" s="27" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="B43" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="C43" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="D43" s="34" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" s="35" t="s">
+        <v>134</v>
+      </c>
+      <c r="B44" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="C44" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="D44" s="36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" s="35" t="s">
+        <v>135</v>
+      </c>
+      <c r="B45" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="C45" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="D45" s="36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" s="35" t="s">
+        <v>137</v>
+      </c>
+      <c r="B46" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="C46" s="32" t="s">
+        <v>113</v>
+      </c>
+      <c r="D46" s="36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" s="35" t="s">
+        <v>136</v>
+      </c>
+      <c r="B47" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="C47" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="D47" s="36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" s="35" t="s">
+        <v>138</v>
+      </c>
+      <c r="B48" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="C48" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="D48" s="36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" s="35" t="s">
+        <v>139</v>
+      </c>
+      <c r="B49" s="32" t="s">
+        <v>68</v>
+      </c>
+      <c r="C49" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="D49" s="36">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" s="35" t="s">
+        <v>140</v>
+      </c>
+      <c r="B50" s="32" t="s">
+        <v>68</v>
+      </c>
+      <c r="C50" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="D50" s="36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51" s="35" t="s">
+        <v>141</v>
+      </c>
+      <c r="B51" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="C51" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="D51" s="36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="B52" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="C52" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="D52" s="36">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53" s="35" t="s">
+        <v>143</v>
+      </c>
+      <c r="B53" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="C53" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="D53" s="36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" s="35" t="s">
+        <v>144</v>
+      </c>
+      <c r="B54" s="32" t="s">
+        <v>82</v>
+      </c>
+      <c r="C54" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="D54" s="36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55" s="35" t="s">
+        <v>145</v>
+      </c>
+      <c r="B55" s="32" t="s">
+        <v>82</v>
+      </c>
+      <c r="C55" s="32" t="s">
+        <v>113</v>
+      </c>
+      <c r="D55" s="36">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Normalisasi_SalesDB_Fran Dello.xlsx
+++ b/Normalisasi_SalesDB_Fran Dello.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Kerjaan\MII\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75741533-A44E-4937-90E3-9C40FA5CCC4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{984D2F59-7BAE-4D74-A97E-23D613C841CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2380,7 +2380,7 @@
         <v>23</v>
       </c>
       <c r="C13" s="33" t="s">
-        <v>133</v>
+        <v>24</v>
       </c>
       <c r="D13" s="28"/>
     </row>

--- a/Normalisasi_SalesDB_Fran Dello.xlsx
+++ b/Normalisasi_SalesDB_Fran Dello.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Kerjaan\MII\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{984D2F59-7BAE-4D74-A97E-23D613C841CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D75183A9-647B-43DE-A336-D17CDA9FA3A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Normalisasi_SalesDB_Fran Dello.xlsx
+++ b/Normalisasi_SalesDB_Fran Dello.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Kerjaan\MII\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D75183A9-647B-43DE-A336-D17CDA9FA3A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{394787D8-C46D-43E1-8E4E-EA6489442BDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -86,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="157">
   <si>
     <t>Latihan Normalisasi SalesDB — dari data faktur (UNF) sampai 3NF</t>
   </si>
@@ -519,9 +519,6 @@
   </si>
   <si>
     <t>TABLE TRANSAKSI</t>
-  </si>
-  <si>
-    <t>Kode Transaksi</t>
   </si>
   <si>
     <t>T01</t>
@@ -572,6 +569,33 @@
 Kode Produk -&gt; Nama Produk, Harga Satuan (Rp) (Partial)
 Kode Kategori -&gt; Nama Kategori (Partial)
 Kode Transaksi -&gt; Qty (Partial)</t>
+  </si>
+  <si>
+    <t>No Faktur (PK)</t>
+  </si>
+  <si>
+    <t>Kode Pelanggan (FK)</t>
+  </si>
+  <si>
+    <t>Kode Transaksi (PK)</t>
+  </si>
+  <si>
+    <t>No Faktur (FK)</t>
+  </si>
+  <si>
+    <t>Kode Produk (FK)</t>
+  </si>
+  <si>
+    <t>Kode Kategori (PK)</t>
+  </si>
+  <si>
+    <t>Kode Produk (PK)</t>
+  </si>
+  <si>
+    <t>Kode Pelanggan (PK)</t>
+  </si>
+  <si>
+    <t>Kode Kategori (FK)</t>
   </si>
 </sst>
 </file>
@@ -798,7 +822,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -892,6 +916,13 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2302,13 +2333,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="4" max="4" width="15.109375" customWidth="1"/>
     <col min="5" max="5" width="11.109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2337,7 +2368,7 @@
         <v>16</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>91</v>
@@ -2348,7 +2379,7 @@
         <v>92</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C7" s="17" t="s">
         <v>93</v>
@@ -2359,7 +2390,7 @@
         <v>94</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -2374,13 +2405,13 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="29" t="s">
-        <v>22</v>
+        <v>148</v>
       </c>
       <c r="B13" s="29" t="s">
         <v>23</v>
       </c>
       <c r="C13" s="33" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="D13" s="28"/>
     </row>
@@ -2457,7 +2488,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="29" t="s">
-        <v>24</v>
+        <v>155</v>
       </c>
       <c r="B22" s="29" t="s">
         <v>25</v>
@@ -2519,9 +2550,9 @@
         <v>130</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A28" s="29" t="s">
-        <v>28</v>
+        <v>154</v>
       </c>
       <c r="B28" s="29" t="s">
         <v>29</v>
@@ -2530,7 +2561,7 @@
         <v>33</v>
       </c>
       <c r="D28" s="29" t="s">
-        <v>30</v>
+        <v>156</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
@@ -2589,7 +2620,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="30" t="s">
         <v>106</v>
       </c>
@@ -2603,7 +2634,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="30" t="s">
         <v>113</v>
       </c>
@@ -2617,20 +2648,20 @@
         <v>110</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="27" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="29" t="s">
-        <v>30</v>
+        <v>153</v>
       </c>
       <c r="B37" s="29" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="30" t="s">
         <v>64</v>
       </c>
@@ -2638,7 +2669,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="30" t="s">
         <v>119</v>
       </c>
@@ -2646,7 +2677,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="30" t="s">
         <v>110</v>
       </c>
@@ -2654,28 +2685,29 @@
         <v>111</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="27" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="34" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="B43" s="29" t="s">
-        <v>22</v>
+        <v>151</v>
       </c>
       <c r="C43" s="29" t="s">
-        <v>28</v>
+        <v>152</v>
       </c>
       <c r="D43" s="34" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E43" s="45"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="35" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B44" s="32" t="s">
         <v>35</v>
@@ -2686,10 +2718,11 @@
       <c r="D44" s="36">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E44" s="46"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="35" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B45" s="32" t="s">
         <v>35</v>
@@ -2700,10 +2733,11 @@
       <c r="D45" s="36">
         <v>2</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E45" s="46"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="35" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B46" s="32" t="s">
         <v>46</v>
@@ -2714,10 +2748,11 @@
       <c r="D46" s="36">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E46" s="46"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="35" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B47" s="32" t="s">
         <v>46</v>
@@ -2728,10 +2763,11 @@
       <c r="D47" s="36">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E47" s="46"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="35" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B48" s="32" t="s">
         <v>57</v>
@@ -2742,10 +2778,11 @@
       <c r="D48" s="36">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E48" s="46"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="35" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B49" s="32" t="s">
         <v>68</v>
@@ -2756,10 +2793,11 @@
       <c r="D49" s="36">
         <v>10</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E49" s="46"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="35" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B50" s="32" t="s">
         <v>68</v>
@@ -2770,10 +2808,11 @@
       <c r="D50" s="36">
         <v>2</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E50" s="47"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="35" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B51" s="32" t="s">
         <v>75</v>
@@ -2785,9 +2824,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="35" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B52" s="32" t="s">
         <v>75</v>
@@ -2799,9 +2838,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="35" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B53" s="32" t="s">
         <v>75</v>
@@ -2813,9 +2852,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="35" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B54" s="32" t="s">
         <v>82</v>
@@ -2827,9 +2866,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="35" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B55" s="32" t="s">
         <v>82</v>

--- a/Normalisasi_SalesDB_Fran Dello.xlsx
+++ b/Normalisasi_SalesDB_Fran Dello.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Kerjaan\MII\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{394787D8-C46D-43E1-8E4E-EA6489442BDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F99964D-AA29-4537-B052-659126B68DCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -822,7 +822,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -909,6 +909,9 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -916,13 +919,6 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1675,20 +1671,20 @@
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A13" s="42" t="s">
+      <c r="A13" s="43" t="s">
         <v>101</v>
       </c>
-      <c r="B13" s="42"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="42"/>
+      <c r="B13" s="43"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="43"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A14" s="43" t="s">
+      <c r="A14" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="B14" s="43"/>
-      <c r="C14" s="43"/>
-      <c r="D14" s="43"/>
+      <c r="B14" s="44"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="20" t="s">
@@ -1699,12 +1695,12 @@
       <c r="D15" s="20"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A16" s="44" t="s">
+      <c r="A16" s="45" t="s">
         <v>104</v>
       </c>
-      <c r="B16" s="44"/>
-      <c r="C16" s="44"/>
-      <c r="D16" s="44"/>
+      <c r="B16" s="45"/>
+      <c r="C16" s="45"/>
+      <c r="D16" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2703,7 +2699,7 @@
       <c r="D43" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="E43" s="45"/>
+      <c r="E43" s="42"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="35" t="s">
@@ -2718,7 +2714,7 @@
       <c r="D44" s="36">
         <v>1</v>
       </c>
-      <c r="E44" s="46"/>
+      <c r="E44" s="27"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="35" t="s">
@@ -2733,7 +2729,7 @@
       <c r="D45" s="36">
         <v>2</v>
       </c>
-      <c r="E45" s="46"/>
+      <c r="E45" s="27"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="35" t="s">
@@ -2748,7 +2744,7 @@
       <c r="D46" s="36">
         <v>1</v>
       </c>
-      <c r="E46" s="46"/>
+      <c r="E46" s="27"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="35" t="s">
@@ -2763,7 +2759,7 @@
       <c r="D47" s="36">
         <v>1</v>
       </c>
-      <c r="E47" s="46"/>
+      <c r="E47" s="27"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="35" t="s">
@@ -2778,7 +2774,7 @@
       <c r="D48" s="36">
         <v>3</v>
       </c>
-      <c r="E48" s="46"/>
+      <c r="E48" s="27"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="35" t="s">
@@ -2793,7 +2789,7 @@
       <c r="D49" s="36">
         <v>10</v>
       </c>
-      <c r="E49" s="46"/>
+      <c r="E49" s="27"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="35" t="s">
@@ -2808,7 +2804,6 @@
       <c r="D50" s="36">
         <v>2</v>
       </c>
-      <c r="E50" s="47"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="35" t="s">

--- a/Normalisasi_SalesDB_Fran Dello.xlsx
+++ b/Normalisasi_SalesDB_Fran Dello.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Kerjaan\MII\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F99964D-AA29-4537-B052-659126B68DCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1DFB1466-45B0-460C-B0B1-B4DE35CAC48B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Petunjuk" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,8 @@
     <sheet name="2_1NF" sheetId="3" r:id="rId3"/>
     <sheet name="3_2NF" sheetId="4" r:id="rId4"/>
     <sheet name="4_3NF" sheetId="5" r:id="rId5"/>
+    <sheet name="ERD" sheetId="6" r:id="rId6"/>
+    <sheet name="ScriptDB" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -86,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="233">
   <si>
     <t>Latihan Normalisasi SalesDB — dari data faktur (UNF) sampai 3NF</t>
   </si>
@@ -596,6 +598,6502 @@
   </si>
   <si>
     <t>Kode Kategori (FK)</t>
+  </si>
+  <si>
+    <r>
+      <t>IF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>DB_ID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'SalesDB'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>IS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>DATABASE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> SalesDB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <t>GO</t>
+  </si>
+  <si>
+    <r>
+      <t>USE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> SalesDB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SCHEMA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> dbo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> dbo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Customer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        CustomerID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>UNIQUEIDENTIFIER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CONSTRAINT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> PK_Customer </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>PRIMARY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>KEY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CustomerID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NVARCHAR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>50</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        Email </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NVARCHAR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>50</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        City </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NVARCHAR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>50</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL,</t>
+    </r>
+  </si>
+  <si>
+    <t>);</t>
+  </si>
+  <si>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>UNIQUE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NONCLUSTERED</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>INDEX</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> UQ_Customer_Email</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>ON</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> dbo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Customer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Email</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>WHERE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Email </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>IS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> dbo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Orderr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        OrderID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>UNIQUEIDENTIFIER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CONSTRAINT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> PK_Orderr </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>PRIMARY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>KEY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>OrderID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        CustomerID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>UNIQUEIDENTIFIER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CONSTRAINT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> FK_Orderr_Customer </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>FOREIGN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>KEY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CustomerID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>REFERENCES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Customer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CustomerID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        PurchaseDate </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>DATETIME2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>DEFAULT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SYSDATETIME</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> dbo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Category</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        CategoryID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>INTEGER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>IDENTITY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CONSTRAINT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> PK_Category </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>PRIMARY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>KEY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CategoryID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        SubCategoryID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>INTEGER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CONSTRAINT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> FK_Category_Category </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>FOREIGN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>KEY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SubCategoryID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>REFERENCES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Category</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CategoryID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> dbo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Product</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        ProductID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>INTEGER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>IDENTITY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CONSTRAINT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> PK_Product </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>PRIMARY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>KEY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>ProductID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        UnitPrice </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>DECIMAL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        Stock </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>INTEGER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        CategoryID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>INTEGER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CONSTRAINT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> FK_Product_Category </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>FOREIGN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>KEY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CategoryID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>REFERENCES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Category</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CategoryID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> dbo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>OrderDetail</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        ProductID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>INTEGER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        OrderID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>UNIQUEIDENTIFIER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        UnitPrice </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>DECIMAL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        Qty </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>INTEGER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">CHECK </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">Qty </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CONSTRAINT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> PK_OrderDetail </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>PRIMARY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>KEY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>ProductID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> OrderID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CONSTRAINT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> FK_OrderDetail_Product </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>FOREIGN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>KEY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>ProductID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>REFERENCES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Product</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>ProductID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CONSTRAINT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> FK_OrderDetail_Orderr </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>FOREIGN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>KEY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>OrderID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>REFERENCES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Orderr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>OrderID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> dbo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>ProductPriceAudit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        AuditID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>INTEGER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>IDENTITY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CONSTRAINT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> PK_ProductPriceAudit </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>PRIMARY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>KEY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>AuditID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        OldPrice </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>DECIMAL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        NewPrice </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>DECIMAL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        ChangeAt </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>DATETIME2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>DEFAULT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SYSDATETIME</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        ChangeBy </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NVARCHAR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>50</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>INSERT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>INTO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> [dbo]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>[Category]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>[Name]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">VALUES  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'Elektronik'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'Alat Tulis'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'Aksesoris Komputer'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>INSERT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>INTO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> [dbo]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">[Customer] </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">VALUES  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NEWID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'Budi Santoso'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'budi@mail.com'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'Jakarta'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NEWID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'Siti Aminah'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'siti@mail.com'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'Bandung'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NEWID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'Andi Wijaya'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'andi@mail.com'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'Surabaya'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>INSERT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>INTO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> [dbo]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>[Product]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>[Name]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> [UnitPrice]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> [Stock]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> [CategoryID]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">VALUES  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'Monitor 24 inci'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 1850000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'Headset USB'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 350000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'Buku Catatan A5'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 25000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'Pulpen Gel (isi 12)'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 48000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'Mouse Wireless'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 150000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'Keyboard Mekanik'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 750000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>INSERT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>INTO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> [dbo]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">[Orderr] </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">VALUES  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NEWID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'6B61022E-6413-4592-80F7-B5C4B23A3D85'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'2026-09-01'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NEWID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'79E1BBA7-ECD9-4A12-9DA4-9BC7F5364275'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'2026-09-10'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NEWID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'2F1D8C33-E98A-407F-8D56-D37265E26495'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'2026-09-12'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NEWID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'6B61022E-6413-4592-80F7-B5C4B23A3D85'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'2026-09-15'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NEWID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'79E1BBA7-ECD9-4A12-9DA4-9BC7F5364275'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'2026-09-18'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NEWID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'2F1D8C33-E98A-407F-8D56-D37265E26495'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'2026-09-20'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>GO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>INSERT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>INTO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> [dbo]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>[OrderDetail]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">VALUES  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'7231ACD2-0FF4-4C83-98FB-A38A30E4CDC7'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 1850000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'7231ACD2-0FF4-4C83-98FB-A38A30E4CDC7'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 150000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'1B0193B5-0492-473B-B238-B587203A1E74'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 750000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'1B0193B5-0492-473B-B238-B587203A1E74'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 150000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'AF64E109-1B66-4BBB-9707-E5CC7DB64A78'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 350000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'0B90AAF0-E480-42DD-B8B7-86CCC27821CB'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 25000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'0B90AAF0-E480-42DD-B8B7-86CCC27821CB'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 48000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'BAD619F3-68DE-4EED-AD11-AB13CBFA14AD'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 350000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'BAD619F3-68DE-4EED-AD11-AB13CBFA14AD'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 25000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'BAD619F3-68DE-4EED-AD11-AB13CBFA14AD'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 48000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'BDAB9B2F-22FB-4991-B7A7-E7C7A117DA1E'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 1850000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'BDAB9B2F-22FB-4991-B7A7-E7C7A117DA1E'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 750000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -605,7 +7103,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -694,6 +7192,36 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Cascadia Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF0000FF"/>
+      <name val="Cascadia Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF00FF"/>
+      <name val="Cascadia Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF808080"/>
+      <name val="Cascadia Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Cascadia Mono"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="9">
@@ -822,7 +7350,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -919,6 +7447,18 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -934,6 +7474,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>470531</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{12DDA3A9-6460-8D8D-05D2-2E20FDE39E40}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="182880"/>
+          <a:ext cx="9614531" cy="3375660"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2339,27 +8928,27 @@
     <col min="5" max="5" width="11.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
         <v>16</v>
       </c>
@@ -2370,7 +8959,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
         <v>92</v>
       </c>
@@ -2381,7 +8970,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
         <v>94</v>
       </c>
@@ -2389,17 +8978,17 @@
         <v>145</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="26" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="29" t="s">
         <v>148</v>
       </c>
@@ -2409,9 +8998,8 @@
       <c r="C13" s="33" t="s">
         <v>149</v>
       </c>
-      <c r="D13" s="28"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="30" t="s">
         <v>35</v>
       </c>
@@ -2422,7 +9010,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="30" t="s">
         <v>46</v>
       </c>
@@ -2432,8 +9020,9 @@
       <c r="C15" s="32" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E15" s="28"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="30" t="s">
         <v>57</v>
       </c>
@@ -2946,4 +9535,566 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C900001B-7AA0-456F-838B-E44E7BF5F926}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96E766B0-23F9-4DBC-A1E9-DFC36797361B}">
+  <dimension ref="B2:B119"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B2" s="46" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B3" s="47" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B4" s="48"/>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B5" s="46" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B6" s="46" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B7" s="48"/>
+    </row>
+    <row r="8" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B8" s="46" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B9" s="48"/>
+    </row>
+    <row r="10" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B10" s="46" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B11" s="48"/>
+    </row>
+    <row r="12" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B12" s="46" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B13" s="46" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B14" s="47" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B15" s="47" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B16" s="47" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B17" s="47" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B18" s="49" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B19" s="48"/>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B20" s="46" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B21" s="48"/>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B22" s="46" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B23" s="47" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B24" s="47" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B25" s="48"/>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B26" s="46" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B27" s="48"/>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B28" s="46" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B29" s="47" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B30" s="47" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B31" s="47" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B32" s="49" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B33" s="48"/>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B34" s="46" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B35" s="48"/>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B36" s="46" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B37" s="47" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B38" s="47" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B39" s="47" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B40" s="49" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B41" s="48"/>
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B42" s="46" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B43" s="48"/>
+    </row>
+    <row r="44" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B44" s="46" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="45" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B45" s="47" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B46" s="47" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B47" s="47" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B48" s="47" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B49" s="47" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B50" s="49" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B51" s="48"/>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B52" s="46" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B53" s="48"/>
+    </row>
+    <row r="54" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B54" s="46" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B55" s="47" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B56" s="47" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="57" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B57" s="47" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="58" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B58" s="47" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="59" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B59" s="47" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="60" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B60" s="47" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="61" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B61" s="47" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="62" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B62" s="49" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="63" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B63" s="48"/>
+    </row>
+    <row r="64" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B64" s="46" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B65" s="48"/>
+    </row>
+    <row r="66" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B66" s="46" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B67" s="47" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="68" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B68" s="47" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B69" s="47" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="70" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B70" s="47" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="71" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B71" s="47" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="72" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B72" s="47" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="73" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B73" s="49" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="74" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B74" s="48"/>
+    </row>
+    <row r="75" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B75" s="46" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="76" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B76" s="48"/>
+    </row>
+    <row r="77" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B77" s="46" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="78" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B78" s="46" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="79" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B79" s="46" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="80" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B80" s="46" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="81" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B81" s="48"/>
+    </row>
+    <row r="82" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B82" s="46" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="83" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B83" s="46" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="84" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B84" s="46" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="85" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B85" s="46" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="86" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B86" s="48"/>
+    </row>
+    <row r="87" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B87" s="46" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="88" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B88" s="48"/>
+    </row>
+    <row r="89" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B89" s="46" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="90" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B90" s="46" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="91" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B91" s="46" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="92" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B92" s="46" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="93" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B93" s="46" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="94" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B94" s="46" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="95" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B95" s="46" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="96" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B96" s="48"/>
+    </row>
+    <row r="97" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B97" s="46" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="98" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B98" s="46" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="99" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B99" s="46" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="100" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B100" s="46" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="101" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B101" s="46" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="102" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B102" s="46" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="103" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B103" s="46" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="104" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B104" s="48"/>
+    </row>
+    <row r="105" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B105" s="46" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="106" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B106" s="48"/>
+    </row>
+    <row r="107" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B107" s="46" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="108" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B108" s="46" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="109" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B109" s="46" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="110" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B110" s="46" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="111" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B111" s="46" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="112" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B112" s="46" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="113" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B113" s="46" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="114" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B114" s="46" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="115" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B115" s="46" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="116" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B116" s="46" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="117" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B117" s="46" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="118" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B118" s="46" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="119" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B119" s="46" t="s">
+        <v>232</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>